--- a/grupos/6ARHV - Estadisticos 20212.xlsx
+++ b/grupos/6ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -182,15 +182,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -215,6 +215,153 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>VOTTE</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>DARIANA MONSERRAT</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>LUIS HUGO</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>MERIELING YAMILETH</t>
+  </si>
+  <si>
+    <t>SAIRA YAMILET</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
     <t>BRISEÑO</t>
   </si>
   <si>
@@ -224,138 +371,42 @@
     <t>DEL CARMEN</t>
   </si>
   <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>DONJUAN</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>QUIAHUA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
     <t>SUSUNAGA</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
     <t>MELCHOR</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILA</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
     <t>TZITZIHUA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
     <t>AURORA</t>
   </si>
   <si>
-    <t>EVELYN AISHA</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
     <t>VANESSA</t>
   </si>
   <si>
@@ -365,15 +416,9 @@
     <t>NAOMI</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>OFELIA</t>
   </si>
   <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
     <t>RAUL ANTONIO</t>
   </si>
   <si>
@@ -383,61 +428,16 @@
     <t>GISELA</t>
   </si>
   <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
     <t>JOSE DANIEL</t>
   </si>
   <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
-  </si>
-  <si>
     <t>MARIAM ABRIL</t>
   </si>
   <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>LUIS HUGO</t>
-  </si>
-  <si>
     <t>GUADALUPE</t>
   </si>
   <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
     <t>NOE</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>MERIELING YAMILETH</t>
-  </si>
-  <si>
-    <t>SAIRA YAMILET</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
   </si>
 </sst>
 </file>
@@ -929,13 +929,13 @@
         <v>-1</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -983,13 +983,13 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
         <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1003,16 +1003,16 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E5">
         <v>9</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>9</v>
@@ -1057,16 +1057,16 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -1083,13 +1083,13 @@
         <v>-1</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -1137,13 +1137,13 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W6">
         <v>-1</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>-1</v>
@@ -1157,16 +1157,16 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E7">
         <v>6</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -1211,16 +1211,16 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1234,16 +1234,16 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G8">
         <v>8</v>
@@ -1288,16 +1288,16 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1311,16 +1311,16 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>7</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>6</v>
@@ -1365,16 +1365,16 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1391,13 +1391,13 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -1445,13 +1445,13 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1468,13 +1468,13 @@
         <v>-1</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>7</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>7</v>
@@ -1522,13 +1522,13 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1542,16 +1542,16 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>8</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -1596,16 +1596,16 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1619,16 +1619,16 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E13">
         <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -1673,16 +1673,16 @@
         <v>7</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>-1</v>
@@ -1696,16 +1696,16 @@
         <v>8</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>7</v>
@@ -1750,16 +1750,16 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1773,16 +1773,16 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>10</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -1827,16 +1827,16 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1850,16 +1850,16 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>7</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>7</v>
@@ -1904,16 +1904,16 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1927,16 +1927,16 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E17">
         <v>7</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>7</v>
@@ -1981,16 +1981,16 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -2004,16 +2004,16 @@
         <v>6</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E18">
         <v>7</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>7</v>
@@ -2058,16 +2058,16 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2084,13 +2084,13 @@
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>8</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -2138,13 +2138,13 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2161,13 +2161,13 @@
         <v>-1</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
         <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G20">
         <v>6</v>
@@ -2215,13 +2215,13 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2235,16 +2235,16 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E21">
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -2289,16 +2289,16 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2315,13 +2315,13 @@
         <v>-1</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>7</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>8</v>
@@ -2369,13 +2369,13 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2392,13 +2392,13 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2446,13 +2446,13 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2466,16 +2466,16 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>10</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -2520,16 +2520,16 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2546,13 +2546,13 @@
         <v>-1</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E25">
         <v>6</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2600,13 +2600,13 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2623,13 +2623,13 @@
         <v>-1</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>5</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -2677,13 +2677,13 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>-1</v>
@@ -2700,13 +2700,13 @@
         <v>-1</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>-1</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -2754,13 +2754,13 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>-1</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>-1</v>
@@ -2774,16 +2774,16 @@
         <v>9</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E28">
         <v>9</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -2828,16 +2828,16 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>9</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -2854,13 +2854,13 @@
         <v>-1</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>5</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -2908,13 +2908,13 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2928,16 +2928,16 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>10</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G30">
         <v>6</v>
@@ -2982,16 +2982,16 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3008,13 +3008,13 @@
         <v>-1</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>5</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G31">
         <v>-1</v>
@@ -3062,13 +3062,13 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>5</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
         <v>-1</v>
@@ -3085,13 +3085,13 @@
         <v>-1</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>-1</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>-1</v>
@@ -3139,13 +3139,13 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>-1</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y32">
         <v>-1</v>
@@ -3162,13 +3162,13 @@
         <v>-1</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E33">
         <v>5</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G33">
         <v>8</v>
@@ -3216,13 +3216,13 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>5</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3239,13 +3239,13 @@
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>8</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>8</v>
@@ -3293,13 +3293,13 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>8</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3313,16 +3313,16 @@
         <v>-1</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E35">
         <v>6</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G35">
         <v>7</v>
@@ -3367,16 +3367,16 @@
         <v>-1</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3393,13 +3393,13 @@
         <v>-1</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>5</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>-1</v>
@@ -3447,13 +3447,13 @@
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>-1</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3521,85 +3521,94 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.2</v>
+      </c>
       <c r="I2">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
         <v>33</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>51.52</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>7.3</v>
+      </c>
       <c r="I3">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>33</v>
       </c>
       <c r="D4">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>69.7</v>
+      </c>
+      <c r="G4">
+        <v>30.3</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="E4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>33</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3608,25 +3617,25 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>69.7</v>
+      </c>
+      <c r="G5">
+        <v>30.3</v>
+      </c>
+      <c r="H5">
+        <v>6.9</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>51.52</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.3</v>
-      </c>
-      <c r="I5">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>48.48</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3700,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3729,39 +3738,39 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920359</v>
+        <v>19330051920358</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920359</v>
+        <v>19330051920358</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -3769,19 +3778,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920359</v>
+        <v>19330051920358</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -3789,119 +3798,119 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920358</v>
+        <v>19330051920360</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920358</v>
+        <v>19330051920360</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920358</v>
+        <v>19330051920360</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920358</v>
+        <v>19330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920358</v>
+        <v>19330051920366</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920360</v>
+        <v>19330051920367</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -3909,99 +3918,99 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920360</v>
+        <v>19330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920360</v>
+        <v>19330051920375</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920360</v>
+        <v>19330051920375</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920360</v>
+        <v>19330051920374</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920456</v>
+        <v>19330051920377</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>54</v>
@@ -4009,79 +4018,79 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920456</v>
+        <v>19330051920377</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920456</v>
+        <v>19330051920378</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920362</v>
+        <v>19330051920378</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920362</v>
+        <v>19330051920382</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
         <v>54</v>
@@ -4089,19 +4098,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920362</v>
+        <v>19330051920382</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
         <v>55</v>
@@ -4109,39 +4118,39 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920426</v>
+        <v>19330051920383</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920426</v>
+        <v>19330051920383</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
         <v>54</v>
@@ -4149,19 +4158,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920426</v>
+        <v>19330051920383</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>55</v>
@@ -4169,99 +4178,99 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920366</v>
+        <v>19330051920386</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920366</v>
+        <v>19330051920386</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920366</v>
+        <v>19330051920386</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920366</v>
+        <v>19330051920386</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920365</v>
+        <v>19330051920436</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
         <v>54</v>
@@ -4269,59 +4278,59 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920365</v>
+        <v>19330051920436</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920365</v>
+        <v>19330051920393</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920368</v>
+        <v>19330051920393</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
         <v>54</v>
@@ -4329,159 +4338,159 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920368</v>
+        <v>19330051920393</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920368</v>
+        <v>19330051920394</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920367</v>
+        <v>19330051920394</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920367</v>
+        <v>19330051920434</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920367</v>
+        <v>19330051920434</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920367</v>
+        <v>19330051920434</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920371</v>
+        <v>19330051920434</v>
       </c>
       <c r="B38" t="s">
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>19330051920371</v>
+        <v>19330051920396</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D39" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
         <v>54</v>
@@ -4489,19 +4498,19 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>19330051920371</v>
+        <v>19330051920396</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D40" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
         <v>55</v>
@@ -4509,79 +4518,79 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>18330051920097</v>
+        <v>19330051920369</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>18330051920097</v>
+        <v>19330051920398</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D42" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>18330051920097</v>
+        <v>19330051920399</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>19330051920372</v>
+        <v>19330051920399</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F44" t="s">
         <v>54</v>
@@ -4589,1662 +4598,22 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>19330051920372</v>
+        <v>19330051920399</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="E45" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920372</v>
-      </c>
-      <c r="B46" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D46" t="s">
-        <v>98</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920373</v>
-      </c>
-      <c r="B47" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" t="s">
-        <v>97</v>
-      </c>
-      <c r="D47" t="s">
-        <v>120</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920373</v>
-      </c>
-      <c r="B48" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D48" t="s">
-        <v>120</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920373</v>
-      </c>
-      <c r="B49" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" t="s">
-        <v>97</v>
-      </c>
-      <c r="D49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920375</v>
-      </c>
-      <c r="B50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" t="s">
-        <v>98</v>
-      </c>
-      <c r="D50" t="s">
-        <v>121</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920375</v>
-      </c>
-      <c r="B51" t="s">
-        <v>75</v>
-      </c>
-      <c r="C51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D51" t="s">
-        <v>121</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920375</v>
-      </c>
-      <c r="B52" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" t="s">
-        <v>121</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920375</v>
-      </c>
-      <c r="B53" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" t="s">
-        <v>121</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920374</v>
-      </c>
-      <c r="B54" t="s">
-        <v>75</v>
-      </c>
-      <c r="C54" t="s">
-        <v>99</v>
-      </c>
-      <c r="D54" t="s">
-        <v>122</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920374</v>
-      </c>
-      <c r="B55" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" t="s">
-        <v>99</v>
-      </c>
-      <c r="D55" t="s">
-        <v>122</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920374</v>
-      </c>
-      <c r="B56" t="s">
-        <v>75</v>
-      </c>
-      <c r="C56" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" t="s">
-        <v>122</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920376</v>
-      </c>
-      <c r="B57" t="s">
-        <v>75</v>
-      </c>
-      <c r="C57" t="s">
-        <v>100</v>
-      </c>
-      <c r="D57" t="s">
-        <v>123</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920376</v>
-      </c>
-      <c r="B58" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" t="s">
-        <v>100</v>
-      </c>
-      <c r="D58" t="s">
-        <v>123</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920376</v>
-      </c>
-      <c r="B59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" t="s">
-        <v>100</v>
-      </c>
-      <c r="D59" t="s">
-        <v>123</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920377</v>
-      </c>
-      <c r="B60" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" t="s">
-        <v>73</v>
-      </c>
-      <c r="D60" t="s">
-        <v>124</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920377</v>
-      </c>
-      <c r="B61" t="s">
-        <v>75</v>
-      </c>
-      <c r="C61" t="s">
-        <v>73</v>
-      </c>
-      <c r="D61" t="s">
-        <v>124</v>
-      </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920377</v>
-      </c>
-      <c r="B62" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" t="s">
-        <v>73</v>
-      </c>
-      <c r="D62" t="s">
-        <v>124</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920377</v>
-      </c>
-      <c r="B63" t="s">
-        <v>75</v>
-      </c>
-      <c r="C63" t="s">
-        <v>73</v>
-      </c>
-      <c r="D63" t="s">
-        <v>124</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920378</v>
-      </c>
-      <c r="B64" t="s">
-        <v>75</v>
-      </c>
-      <c r="C64" t="s">
-        <v>75</v>
-      </c>
-      <c r="D64" t="s">
-        <v>125</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920378</v>
-      </c>
-      <c r="B65" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" t="s">
-        <v>75</v>
-      </c>
-      <c r="D65" t="s">
-        <v>125</v>
-      </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920378</v>
-      </c>
-      <c r="B66" t="s">
-        <v>75</v>
-      </c>
-      <c r="C66" t="s">
-        <v>75</v>
-      </c>
-      <c r="D66" t="s">
-        <v>125</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920378</v>
-      </c>
-      <c r="B67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" t="s">
-        <v>75</v>
-      </c>
-      <c r="D67" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920381</v>
-      </c>
-      <c r="B68" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" t="s">
-        <v>74</v>
-      </c>
-      <c r="D68" t="s">
-        <v>126</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920381</v>
-      </c>
-      <c r="B69" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" t="s">
-        <v>126</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920381</v>
-      </c>
-      <c r="B70" t="s">
-        <v>76</v>
-      </c>
-      <c r="C70" t="s">
-        <v>74</v>
-      </c>
-      <c r="D70" t="s">
-        <v>126</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920382</v>
-      </c>
-      <c r="B71" t="s">
-        <v>77</v>
-      </c>
-      <c r="C71" t="s">
-        <v>92</v>
-      </c>
-      <c r="D71" t="s">
-        <v>127</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920382</v>
-      </c>
-      <c r="B72" t="s">
-        <v>77</v>
-      </c>
-      <c r="C72" t="s">
-        <v>92</v>
-      </c>
-      <c r="D72" t="s">
-        <v>127</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920382</v>
-      </c>
-      <c r="B73" t="s">
-        <v>77</v>
-      </c>
-      <c r="C73" t="s">
-        <v>92</v>
-      </c>
-      <c r="D73" t="s">
-        <v>127</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920382</v>
-      </c>
-      <c r="B74" t="s">
-        <v>77</v>
-      </c>
-      <c r="C74" t="s">
-        <v>92</v>
-      </c>
-      <c r="D74" t="s">
-        <v>127</v>
-      </c>
-      <c r="E74" t="s">
-        <v>5</v>
-      </c>
-      <c r="F74" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920383</v>
-      </c>
-      <c r="B75" t="s">
-        <v>78</v>
-      </c>
-      <c r="C75" t="s">
-        <v>101</v>
-      </c>
-      <c r="D75" t="s">
-        <v>128</v>
-      </c>
-      <c r="E75" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920383</v>
-      </c>
-      <c r="B76" t="s">
-        <v>78</v>
-      </c>
-      <c r="C76" t="s">
-        <v>101</v>
-      </c>
-      <c r="D76" t="s">
-        <v>128</v>
-      </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920383</v>
-      </c>
-      <c r="B77" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" t="s">
-        <v>101</v>
-      </c>
-      <c r="D77" t="s">
-        <v>128</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920383</v>
-      </c>
-      <c r="B78" t="s">
-        <v>78</v>
-      </c>
-      <c r="C78" t="s">
-        <v>101</v>
-      </c>
-      <c r="D78" t="s">
-        <v>128</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920383</v>
-      </c>
-      <c r="B79" t="s">
-        <v>78</v>
-      </c>
-      <c r="C79" t="s">
-        <v>101</v>
-      </c>
-      <c r="D79" t="s">
-        <v>128</v>
-      </c>
-      <c r="E79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>19330051920386</v>
-      </c>
-      <c r="B80" t="s">
-        <v>79</v>
-      </c>
-      <c r="C80" t="s">
-        <v>102</v>
-      </c>
-      <c r="D80" t="s">
-        <v>129</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>19330051920386</v>
-      </c>
-      <c r="B81" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" t="s">
-        <v>102</v>
-      </c>
-      <c r="D81" t="s">
-        <v>129</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>19330051920386</v>
-      </c>
-      <c r="B82" t="s">
-        <v>79</v>
-      </c>
-      <c r="C82" t="s">
-        <v>102</v>
-      </c>
-      <c r="D82" t="s">
-        <v>129</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>19330051920386</v>
-      </c>
-      <c r="B83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C83" t="s">
-        <v>102</v>
-      </c>
-      <c r="D83" t="s">
-        <v>129</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>19330051920386</v>
-      </c>
-      <c r="B84" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" t="s">
-        <v>102</v>
-      </c>
-      <c r="D84" t="s">
-        <v>129</v>
-      </c>
-      <c r="E84" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>19330051920386</v>
-      </c>
-      <c r="B85" t="s">
-        <v>79</v>
-      </c>
-      <c r="C85" t="s">
-        <v>102</v>
-      </c>
-      <c r="D85" t="s">
-        <v>129</v>
-      </c>
-      <c r="E85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>19330051920389</v>
-      </c>
-      <c r="B86" t="s">
-        <v>80</v>
-      </c>
-      <c r="C86" t="s">
-        <v>63</v>
-      </c>
-      <c r="D86" t="s">
-        <v>130</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>19330051920389</v>
-      </c>
-      <c r="B87" t="s">
-        <v>80</v>
-      </c>
-      <c r="C87" t="s">
-        <v>63</v>
-      </c>
-      <c r="D87" t="s">
-        <v>130</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>19330051920389</v>
-      </c>
-      <c r="B88" t="s">
-        <v>80</v>
-      </c>
-      <c r="C88" t="s">
-        <v>63</v>
-      </c>
-      <c r="D88" t="s">
-        <v>130</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>19330051920436</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-      <c r="C89" t="s">
-        <v>96</v>
-      </c>
-      <c r="D89" t="s">
-        <v>131</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920436</v>
-      </c>
-      <c r="B90" t="s">
-        <v>81</v>
-      </c>
-      <c r="C90" t="s">
-        <v>96</v>
-      </c>
-      <c r="D90" t="s">
-        <v>131</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920436</v>
-      </c>
-      <c r="B91" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" t="s">
-        <v>96</v>
-      </c>
-      <c r="D91" t="s">
-        <v>131</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920436</v>
-      </c>
-      <c r="B92" t="s">
-        <v>81</v>
-      </c>
-      <c r="C92" t="s">
-        <v>96</v>
-      </c>
-      <c r="D92" t="s">
-        <v>131</v>
-      </c>
-      <c r="E92" t="s">
-        <v>5</v>
-      </c>
-      <c r="F92" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920391</v>
-      </c>
-      <c r="B93" t="s">
-        <v>82</v>
-      </c>
-      <c r="C93" t="s">
-        <v>103</v>
-      </c>
-      <c r="D93" t="s">
-        <v>132</v>
-      </c>
-      <c r="E93" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920391</v>
-      </c>
-      <c r="B94" t="s">
-        <v>82</v>
-      </c>
-      <c r="C94" t="s">
-        <v>103</v>
-      </c>
-      <c r="D94" t="s">
-        <v>132</v>
-      </c>
-      <c r="E94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920391</v>
-      </c>
-      <c r="B95" t="s">
-        <v>82</v>
-      </c>
-      <c r="C95" t="s">
-        <v>103</v>
-      </c>
-      <c r="D95" t="s">
-        <v>132</v>
-      </c>
-      <c r="E95" t="s">
-        <v>6</v>
-      </c>
-      <c r="F95" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920393</v>
-      </c>
-      <c r="B96" t="s">
-        <v>83</v>
-      </c>
-      <c r="C96" t="s">
-        <v>70</v>
-      </c>
-      <c r="D96" t="s">
-        <v>133</v>
-      </c>
-      <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>19330051920393</v>
-      </c>
-      <c r="B97" t="s">
-        <v>83</v>
-      </c>
-      <c r="C97" t="s">
-        <v>70</v>
-      </c>
-      <c r="D97" t="s">
-        <v>133</v>
-      </c>
-      <c r="E97" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>19330051920393</v>
-      </c>
-      <c r="B98" t="s">
-        <v>83</v>
-      </c>
-      <c r="C98" t="s">
-        <v>70</v>
-      </c>
-      <c r="D98" t="s">
-        <v>133</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>19330051920393</v>
-      </c>
-      <c r="B99" t="s">
-        <v>83</v>
-      </c>
-      <c r="C99" t="s">
-        <v>70</v>
-      </c>
-      <c r="D99" t="s">
-        <v>133</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>19330051920393</v>
-      </c>
-      <c r="B100" t="s">
-        <v>83</v>
-      </c>
-      <c r="C100" t="s">
-        <v>70</v>
-      </c>
-      <c r="D100" t="s">
-        <v>133</v>
-      </c>
-      <c r="E100" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>19330051920394</v>
-      </c>
-      <c r="B101" t="s">
-        <v>84</v>
-      </c>
-      <c r="C101" t="s">
-        <v>104</v>
-      </c>
-      <c r="D101" t="s">
-        <v>134</v>
-      </c>
-      <c r="E101" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>19330051920394</v>
-      </c>
-      <c r="B102" t="s">
-        <v>84</v>
-      </c>
-      <c r="C102" t="s">
-        <v>104</v>
-      </c>
-      <c r="D102" t="s">
-        <v>134</v>
-      </c>
-      <c r="E102" t="s">
-        <v>7</v>
-      </c>
-      <c r="F102" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>19330051920394</v>
-      </c>
-      <c r="B103" t="s">
-        <v>84</v>
-      </c>
-      <c r="C103" t="s">
-        <v>104</v>
-      </c>
-      <c r="D103" t="s">
-        <v>134</v>
-      </c>
-      <c r="E103" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>19330051920394</v>
-      </c>
-      <c r="B104" t="s">
-        <v>84</v>
-      </c>
-      <c r="C104" t="s">
-        <v>104</v>
-      </c>
-      <c r="D104" t="s">
-        <v>134</v>
-      </c>
-      <c r="E104" t="s">
-        <v>5</v>
-      </c>
-      <c r="F104" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>19330051920434</v>
-      </c>
-      <c r="B105" t="s">
-        <v>83</v>
-      </c>
-      <c r="C105" t="s">
-        <v>105</v>
-      </c>
-      <c r="D105" t="s">
-        <v>135</v>
-      </c>
-      <c r="E105" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>19330051920434</v>
-      </c>
-      <c r="B106" t="s">
-        <v>83</v>
-      </c>
-      <c r="C106" t="s">
-        <v>105</v>
-      </c>
-      <c r="D106" t="s">
-        <v>135</v>
-      </c>
-      <c r="E106" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>19330051920434</v>
-      </c>
-      <c r="B107" t="s">
-        <v>83</v>
-      </c>
-      <c r="C107" t="s">
-        <v>105</v>
-      </c>
-      <c r="D107" t="s">
-        <v>135</v>
-      </c>
-      <c r="E107" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>19330051920434</v>
-      </c>
-      <c r="B108" t="s">
-        <v>83</v>
-      </c>
-      <c r="C108" t="s">
-        <v>105</v>
-      </c>
-      <c r="D108" t="s">
-        <v>135</v>
-      </c>
-      <c r="E108" t="s">
-        <v>8</v>
-      </c>
-      <c r="F108" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>19330051920434</v>
-      </c>
-      <c r="B109" t="s">
-        <v>83</v>
-      </c>
-      <c r="C109" t="s">
-        <v>105</v>
-      </c>
-      <c r="D109" t="s">
-        <v>135</v>
-      </c>
-      <c r="E109" t="s">
-        <v>6</v>
-      </c>
-      <c r="F109" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>19330051920434</v>
-      </c>
-      <c r="B110" t="s">
-        <v>83</v>
-      </c>
-      <c r="C110" t="s">
-        <v>105</v>
-      </c>
-      <c r="D110" t="s">
-        <v>135</v>
-      </c>
-      <c r="E110" t="s">
-        <v>5</v>
-      </c>
-      <c r="F110" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>19330051920396</v>
-      </c>
-      <c r="B111" t="s">
-        <v>85</v>
-      </c>
-      <c r="C111" t="s">
-        <v>106</v>
-      </c>
-      <c r="D111" t="s">
-        <v>136</v>
-      </c>
-      <c r="E111" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>19330051920396</v>
-      </c>
-      <c r="B112" t="s">
-        <v>85</v>
-      </c>
-      <c r="C112" t="s">
-        <v>106</v>
-      </c>
-      <c r="D112" t="s">
-        <v>136</v>
-      </c>
-      <c r="E112" t="s">
-        <v>7</v>
-      </c>
-      <c r="F112" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>19330051920396</v>
-      </c>
-      <c r="B113" t="s">
-        <v>85</v>
-      </c>
-      <c r="C113" t="s">
-        <v>106</v>
-      </c>
-      <c r="D113" t="s">
-        <v>136</v>
-      </c>
-      <c r="E113" t="s">
-        <v>6</v>
-      </c>
-      <c r="F113" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>19330051920396</v>
-      </c>
-      <c r="B114" t="s">
-        <v>85</v>
-      </c>
-      <c r="C114" t="s">
-        <v>106</v>
-      </c>
-      <c r="D114" t="s">
-        <v>136</v>
-      </c>
-      <c r="E114" t="s">
-        <v>5</v>
-      </c>
-      <c r="F114" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>19330051920369</v>
-      </c>
-      <c r="B115" t="s">
-        <v>86</v>
-      </c>
-      <c r="C115" t="s">
-        <v>107</v>
-      </c>
-      <c r="D115" t="s">
-        <v>137</v>
-      </c>
-      <c r="E115" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>19330051920369</v>
-      </c>
-      <c r="B116" t="s">
-        <v>86</v>
-      </c>
-      <c r="C116" t="s">
-        <v>107</v>
-      </c>
-      <c r="D116" t="s">
-        <v>137</v>
-      </c>
-      <c r="E116" t="s">
-        <v>7</v>
-      </c>
-      <c r="F116" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>19330051920369</v>
-      </c>
-      <c r="B117" t="s">
-        <v>86</v>
-      </c>
-      <c r="C117" t="s">
-        <v>107</v>
-      </c>
-      <c r="D117" t="s">
-        <v>137</v>
-      </c>
-      <c r="E117" t="s">
-        <v>10</v>
-      </c>
-      <c r="F117" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>19330051920369</v>
-      </c>
-      <c r="B118" t="s">
-        <v>86</v>
-      </c>
-      <c r="C118" t="s">
-        <v>107</v>
-      </c>
-      <c r="D118" t="s">
-        <v>137</v>
-      </c>
-      <c r="E118" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>19330051920398</v>
-      </c>
-      <c r="B119" t="s">
-        <v>87</v>
-      </c>
-      <c r="C119" t="s">
-        <v>79</v>
-      </c>
-      <c r="D119" t="s">
-        <v>138</v>
-      </c>
-      <c r="E119" t="s">
-        <v>9</v>
-      </c>
-      <c r="F119" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>19330051920398</v>
-      </c>
-      <c r="B120" t="s">
-        <v>87</v>
-      </c>
-      <c r="C120" t="s">
-        <v>79</v>
-      </c>
-      <c r="D120" t="s">
-        <v>138</v>
-      </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>19330051920398</v>
-      </c>
-      <c r="B121" t="s">
-        <v>87</v>
-      </c>
-      <c r="C121" t="s">
-        <v>79</v>
-      </c>
-      <c r="D121" t="s">
-        <v>138</v>
-      </c>
-      <c r="E121" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>19330051920398</v>
-      </c>
-      <c r="B122" t="s">
-        <v>87</v>
-      </c>
-      <c r="C122" t="s">
-        <v>79</v>
-      </c>
-      <c r="D122" t="s">
-        <v>138</v>
-      </c>
-      <c r="E122" t="s">
-        <v>5</v>
-      </c>
-      <c r="F122" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>19330051920399</v>
-      </c>
-      <c r="B123" t="s">
-        <v>88</v>
-      </c>
-      <c r="C123" t="s">
-        <v>108</v>
-      </c>
-      <c r="D123" t="s">
-        <v>139</v>
-      </c>
-      <c r="E123" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>19330051920399</v>
-      </c>
-      <c r="B124" t="s">
-        <v>88</v>
-      </c>
-      <c r="C124" t="s">
-        <v>108</v>
-      </c>
-      <c r="D124" t="s">
-        <v>139</v>
-      </c>
-      <c r="E124" t="s">
-        <v>7</v>
-      </c>
-      <c r="F124" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>19330051920399</v>
-      </c>
-      <c r="B125" t="s">
-        <v>88</v>
-      </c>
-      <c r="C125" t="s">
-        <v>108</v>
-      </c>
-      <c r="D125" t="s">
-        <v>139</v>
-      </c>
-      <c r="E125" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>19330051920399</v>
-      </c>
-      <c r="B126" t="s">
-        <v>88</v>
-      </c>
-      <c r="C126" t="s">
-        <v>108</v>
-      </c>
-      <c r="D126" t="s">
-        <v>139</v>
-      </c>
-      <c r="E126" t="s">
-        <v>6</v>
-      </c>
-      <c r="F126" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>19330051920399</v>
-      </c>
-      <c r="B127" t="s">
-        <v>88</v>
-      </c>
-      <c r="C127" t="s">
-        <v>108</v>
-      </c>
-      <c r="D127" t="s">
-        <v>139</v>
-      </c>
-      <c r="E127" t="s">
-        <v>5</v>
-      </c>
-      <c r="F127" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -6283,16 +4652,16 @@
         <v>19330051920386</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -6300,16 +4669,16 @@
         <v>19330051920434</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -6320,13 +4689,13 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6337,13 +4706,13 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -6351,16 +4720,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6368,16 +4737,16 @@
         <v>19330051920393</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6385,16 +4754,16 @@
         <v>19330051920399</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6402,16 +4771,16 @@
         <v>19330051920366</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6419,16 +4788,16 @@
         <v>19330051920367</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6436,16 +4805,16 @@
         <v>19330051920375</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6453,16 +4822,16 @@
         <v>19330051920377</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6470,16 +4839,16 @@
         <v>19330051920378</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6487,16 +4856,16 @@
         <v>19330051920382</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6504,16 +4873,16 @@
         <v>19330051920436</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6521,16 +4890,16 @@
         <v>19330051920394</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6538,237 +4907,237 @@
         <v>19330051920396</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920369</v>
+        <v>19330051920374</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920398</v>
+        <v>19330051920369</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920359</v>
+        <v>19330051920398</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
         <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920456</v>
+        <v>19330051920359</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920362</v>
+        <v>19330051920456</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920426</v>
+        <v>19330051920362</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920365</v>
+        <v>19330051920426</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920368</v>
+        <v>19330051920365</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920371</v>
+        <v>19330051920368</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>18330051920097</v>
+        <v>19330051920371</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920372</v>
+        <v>18330051920097</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920373</v>
+        <v>19330051920372</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920374</v>
+        <v>19330051920373</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -6776,16 +5145,16 @@
         <v>19330051920376</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -6793,16 +5162,16 @@
         <v>19330051920381</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6810,16 +5179,16 @@
         <v>19330051920389</v>
       </c>
       <c r="B33" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
         <v>63</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -6827,16 +5196,16 @@
         <v>19330051920391</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6846,7 +5215,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6876,6 +5245,305 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920366</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920366</v>
+      </c>
+      <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920367</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920367</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920375</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920375</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920382</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920382</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920396</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920396</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920374</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920369</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920398</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/6ARHV - Estadisticos 20212.xlsx
+++ b/grupos/6ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -182,15 +182,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
@@ -209,34 +209,94 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>VOTTE</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>LUIS HUGO</t>
+  </si>
+  <si>
+    <t>SAIRA YAMILET</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>BRETON</t>
+    <t>BRISEÑO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>DEL CARMEN</t>
   </si>
   <si>
     <t>CRISTOBAL</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>DONJUAN</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>QUIAHUA</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
+    <t>RIOS</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -251,19 +311,28 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>VICENTE</t>
+    <t>SUSUNAGA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>BRUNO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -272,84 +341,96 @@
     <t>AGUILA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>CORTES</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>TZITZIHUA</t>
   </si>
   <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>VOTTE</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>VERGEL</t>
+    <t>AURORA</t>
   </si>
   <si>
     <t>EVELYN AISHA</t>
   </si>
   <si>
-    <t>AMYRA NAHOMY</t>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
   </si>
   <si>
     <t>DANIELA</t>
   </si>
   <si>
+    <t>OFELIA</t>
+  </si>
+  <si>
     <t>ZURI SADAY</t>
   </si>
   <si>
+    <t>RAUL ANTONIO</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>GISELA</t>
+  </si>
+  <si>
     <t>MARIA GUADALUPE</t>
   </si>
   <si>
     <t>JESUS</t>
   </si>
   <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
     <t>PERLA</t>
   </si>
   <si>
     <t>DARIANA MONSERRAT</t>
   </si>
   <si>
+    <t>MARIAM ABRIL</t>
+  </si>
+  <si>
     <t>LUCERO</t>
   </si>
   <si>
     <t>FATIMA</t>
   </si>
   <si>
-    <t>LUIS HUGO</t>
+    <t>GUADALUPE</t>
   </si>
   <si>
     <t>ASTRID</t>
   </si>
   <si>
+    <t>NOE</t>
+  </si>
+  <si>
     <t>ITZEL ISABEL</t>
   </si>
   <si>
     <t>MERIELING YAMILETH</t>
   </si>
   <si>
-    <t>SAIRA YAMILET</t>
-  </si>
-  <si>
     <t>ELIZABETH</t>
   </si>
   <si>
@@ -357,87 +438,6 @@
   </si>
   <si>
     <t>VALERIA</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>BRISEÑO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DONJUAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SUSUNAGA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>AURORA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>OFELIA</t>
-  </si>
-  <si>
-    <t>RAUL ANTONIO</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>GISELA</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>MARIAM ABRIL</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>NOE</t>
   </si>
 </sst>
 </file>
@@ -923,10 +923,10 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -956,7 +956,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -977,10 +977,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -992,7 +992,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1021,7 +1021,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -1033,7 +1033,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1057,7 +1057,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1069,7 +1069,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1080,7 +1080,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1098,7 +1098,7 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1134,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>5</v>
@@ -1175,7 +1175,7 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1187,7 +1187,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1211,7 +1211,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1223,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1252,7 +1252,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1264,7 +1264,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1300,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1329,7 +1329,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1341,7 +1341,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1377,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1385,10 +1385,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1439,10 +1439,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1454,7 +1454,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1462,10 +1462,10 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1483,7 +1483,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1495,7 +1495,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1516,10 +1516,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1560,7 +1560,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1608,7 +1608,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1631,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1649,7 +1649,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1685,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1714,7 +1714,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1726,7 +1726,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1762,7 +1762,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1791,7 +1791,7 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1803,7 +1803,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1868,7 +1868,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1880,7 +1880,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1916,7 +1916,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1945,7 +1945,7 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1957,7 +1957,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1993,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2022,7 +2022,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -2034,7 +2034,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2058,7 +2058,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2081,7 +2081,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -2099,7 +2099,7 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2111,7 +2111,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2135,7 +2135,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2147,7 +2147,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2155,10 +2155,10 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2176,7 +2176,7 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2188,7 +2188,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2209,10 +2209,10 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2253,7 +2253,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2265,7 +2265,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2289,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2301,7 +2301,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2309,10 +2309,10 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>5</v>
@@ -2330,7 +2330,7 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2342,7 +2342,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2363,10 +2363,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2386,10 +2386,10 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -2407,7 +2407,7 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2419,7 +2419,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2440,10 +2440,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2455,7 +2455,7 @@
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2484,7 +2484,7 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2496,7 +2496,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2520,7 +2520,7 @@
         <v>7</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2532,7 +2532,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2540,10 +2540,10 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>7</v>
@@ -2573,7 +2573,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2594,10 +2594,10 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2617,10 +2617,10 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>5</v>
@@ -2632,7 +2632,7 @@
         <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2650,7 +2650,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2671,10 +2671,10 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2686,7 +2686,7 @@
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2694,10 +2694,10 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -2715,7 +2715,7 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2748,10 +2748,10 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2792,7 +2792,7 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2804,7 +2804,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2840,7 +2840,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2848,10 +2848,10 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -2881,7 +2881,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2902,10 +2902,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2917,7 +2917,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2946,7 +2946,7 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -3002,10 +3002,10 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -3017,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3035,7 +3035,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3056,10 +3056,10 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
         <v>5</v>
@@ -3071,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3079,10 +3079,10 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -3094,13 +3094,13 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3133,10 +3133,10 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3148,7 +3148,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3156,10 +3156,10 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3189,7 +3189,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3210,10 +3210,10 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3225,7 +3225,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3233,10 +3233,10 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -3254,7 +3254,7 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3287,10 +3287,10 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3310,7 +3310,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -3331,7 +3331,7 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3343,7 +3343,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3364,7 +3364,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3379,7 +3379,7 @@
         <v>9</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3387,10 +3387,10 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>5</v>
@@ -3408,7 +3408,7 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3441,10 +3441,10 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3521,65 +3521,65 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>69.7</v>
+      </c>
+      <c r="G2">
+        <v>30.3</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>48.48</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.2</v>
-      </c>
-      <c r="I2">
-        <v>17</v>
-      </c>
-      <c r="J2">
-        <v>51.52</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3">
         <v>33</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>69.7</v>
+      </c>
+      <c r="G3">
+        <v>30.3</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>51.52</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.3</v>
-      </c>
-      <c r="I3">
-        <v>16</v>
-      </c>
-      <c r="J3">
-        <v>48.48</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4">
         <v>33</v>
@@ -3597,7 +3597,7 @@
         <v>30.3</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3629,7 +3629,7 @@
         <v>30.3</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3681,25 +3681,25 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>75.76000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>24.24</v>
+        <v>9.09</v>
       </c>
     </row>
   </sheetData>
@@ -3709,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3738,16 +3738,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920358</v>
+        <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -3758,76 +3758,76 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920358</v>
+        <v>19330051920360</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920358</v>
+        <v>19330051920386</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920360</v>
+        <v>19330051920386</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920360</v>
+        <v>19330051920434</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -3838,782 +3838,22 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920360</v>
+        <v>19330051920399</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920366</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920366</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920367</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920367</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920375</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920375</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920374</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920377</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920377</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920378</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920378</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920382</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920382</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920383</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920383</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920383</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920386</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920386</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920386</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920386</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920436</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>106</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920436</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" t="s">
-        <v>106</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920393</v>
-      </c>
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" t="s">
-        <v>107</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920393</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920393</v>
-      </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920394</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-      <c r="D33" t="s">
-        <v>108</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920394</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920434</v>
-      </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920434</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s">
-        <v>91</v>
-      </c>
-      <c r="D36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920434</v>
-      </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920434</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" t="s">
-        <v>109</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920396</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
-      </c>
-      <c r="D39" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920396</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" t="s">
-        <v>110</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920369</v>
-      </c>
-      <c r="B41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920398</v>
-      </c>
-      <c r="B42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" t="s">
-        <v>70</v>
-      </c>
-      <c r="D42" t="s">
-        <v>112</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920399</v>
-      </c>
-      <c r="B43" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" t="s">
-        <v>94</v>
-      </c>
-      <c r="D43" t="s">
-        <v>113</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920399</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" t="s">
-        <v>94</v>
-      </c>
-      <c r="D44" t="s">
-        <v>113</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920399</v>
-      </c>
-      <c r="B45" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" t="s">
-        <v>113</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4649,339 +3889,339 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920386</v>
+        <v>19330051920360</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920434</v>
+        <v>19330051920386</v>
       </c>
       <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
         <v>72</v>
       </c>
-      <c r="C3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D3" t="s">
-        <v>109</v>
-      </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920358</v>
+        <v>19330051920434</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920360</v>
+        <v>19330051920399</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920383</v>
+        <v>19330051920359</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920393</v>
+        <v>19330051920358</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920399</v>
+        <v>19330051920456</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920366</v>
+        <v>19330051920362</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920367</v>
+        <v>19330051920426</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920375</v>
+        <v>19330051920366</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920377</v>
+        <v>19330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920378</v>
+        <v>19330051920368</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920382</v>
+        <v>19330051920367</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920436</v>
+        <v>19330051920371</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920394</v>
+        <v>18330051920097</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920396</v>
+        <v>19330051920372</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920374</v>
+        <v>19330051920373</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920369</v>
+        <v>19330051920375</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920398</v>
+        <v>19330051920374</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920359</v>
+        <v>19330051920376</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4989,16 +4229,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920456</v>
+        <v>19330051920377</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5006,16 +4246,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920362</v>
+        <v>19330051920378</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5023,16 +4263,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920426</v>
+        <v>19330051920381</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
         <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5040,16 +4280,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920365</v>
+        <v>19330051920382</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5057,16 +4297,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920368</v>
+        <v>19330051920383</v>
       </c>
       <c r="B26" t="s">
         <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5074,16 +4314,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920371</v>
+        <v>19330051920389</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5091,16 +4331,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>18330051920097</v>
+        <v>19330051920436</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5108,16 +4348,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920372</v>
+        <v>19330051920391</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5125,13 +4365,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920373</v>
+        <v>19330051920393</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="D30" t="s">
         <v>135</v>
@@ -5142,13 +4382,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920376</v>
+        <v>19330051920394</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
@@ -5159,13 +4399,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920381</v>
+        <v>19330051920396</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
         <v>137</v>
@@ -5176,13 +4416,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920389</v>
+        <v>19330051920369</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
         <v>138</v>
@@ -5193,13 +4433,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920391</v>
+        <v>19330051920398</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="D34" t="s">
         <v>139</v>
@@ -5215,7 +4455,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5247,140 +4487,140 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920366</v>
+        <v>19330051920377</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920366</v>
+        <v>19330051920377</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920367</v>
+        <v>19330051920378</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920367</v>
+        <v>19330051920378</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920375</v>
+        <v>19330051920366</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>55</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920375</v>
+        <v>19330051920367</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5388,45 +4628,45 @@
         <v>19330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920382</v>
+        <v>19330051920394</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5434,114 +4674,45 @@
         <v>19330051920396</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920396</v>
+        <v>19330051920398</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920374</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920369</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920398</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ARHV - Estadisticos 20212.xlsx
+++ b/grupos/6ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -182,16 +182,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>Gaspar Velazco Juan Francisco</t>
@@ -941,19 +941,19 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -1018,19 +1018,19 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1054,7 +1054,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -1101,13 +1101,13 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1172,19 +1172,19 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1208,19 +1208,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>7</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1249,19 +1249,19 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1285,19 +1285,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>7</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1332,13 +1332,13 @@
         <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>7</v>
@@ -1368,13 +1368,13 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1409,13 +1409,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1445,13 +1445,13 @@
         <v>5</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1480,19 +1480,19 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1528,7 +1528,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1557,19 +1557,19 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -1593,19 +1593,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>6</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1640,13 +1640,13 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -1711,19 +1711,19 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1756,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1788,19 +1788,19 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>8</v>
@@ -1824,7 +1824,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1865,19 +1865,19 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -1907,13 +1907,13 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1942,19 +1942,19 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -1984,13 +1984,13 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2025,13 +2025,13 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>7</v>
@@ -2061,13 +2061,13 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2096,19 +2096,19 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2132,19 +2132,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>10</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2173,19 +2173,19 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>8</v>
@@ -2209,19 +2209,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>8</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>7</v>
@@ -2250,19 +2250,19 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2292,13 +2292,13 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2333,13 +2333,13 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2369,13 +2369,13 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2404,19 +2404,19 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -2440,19 +2440,19 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>6</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2481,19 +2481,19 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -2517,19 +2517,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>7</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2558,19 +2558,19 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2594,19 +2594,19 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>5</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>6</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2641,13 +2641,13 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>7</v>
@@ -2677,13 +2677,13 @@
         <v>5</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2718,13 +2718,13 @@
         <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2789,19 +2789,19 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2831,13 +2831,13 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2866,19 +2866,19 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>7</v>
@@ -2949,13 +2949,13 @@
         <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2988,7 +2988,7 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3020,19 +3020,19 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -3062,7 +3062,7 @@
         <v>5</v>
       </c>
       <c r="V31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>5</v>
@@ -3097,19 +3097,19 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3174,19 +3174,19 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -3210,19 +3210,19 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>8</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>5</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3251,19 +3251,19 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3296,7 +3296,7 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
@@ -3334,13 +3334,13 @@
         <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>8</v>
@@ -3373,7 +3373,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3411,13 +3411,13 @@
         <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3521,19 +3521,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>69.7</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
-        <v>30.3</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3">
         <v>33</v>
@@ -3565,7 +3565,7 @@
         <v>30.3</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3576,60 +3576,60 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4">
         <v>33</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="G4">
-        <v>30.3</v>
+        <v>18.18</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>33</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="G5">
-        <v>30.3</v>
+        <v>21.21</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3649,25 +3649,25 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>6</v>
       </c>
       <c r="F6">
-        <v>72.73</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G6">
         <v>18.18</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3773,7 +3773,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3813,7 +3813,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3833,7 +3833,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4455,7 +4455,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4487,22 +4487,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920377</v>
+        <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4510,19 +4510,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920377</v>
+        <v>19330051920367</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -4533,19 +4533,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920378</v>
+        <v>19330051920375</v>
       </c>
       <c r="B4" t="s">
         <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>54</v>
@@ -4556,22 +4556,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920378</v>
+        <v>19330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4579,22 +4579,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920366</v>
+        <v>19330051920394</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4602,22 +4602,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920367</v>
+        <v>19330051920396</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4625,93 +4625,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920382</v>
+        <v>19330051920398</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920394</v>
-      </c>
-      <c r="B9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920396</v>
-      </c>
-      <c r="B10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920398</v>
-      </c>
-      <c r="B11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHV - Estadisticos 20212.xlsx
+++ b/grupos/6ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -218,226 +218,226 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>VOTTE</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>LUIS HUGO</t>
+  </si>
+  <si>
+    <t>SAIRA YAMILET</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>BRISEÑO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DONJUAN</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ZARATE</t>
   </si>
   <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>VOTTE</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>SUSUNAGA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>VERGEL</t>
   </si>
   <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>LUIS HUGO</t>
-  </si>
-  <si>
-    <t>SAIRA YAMILET</t>
+    <t>AURORA</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>OFELIA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>RAUL ANTONIO</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>GISELA</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>DARIANA MONSERRAT</t>
+  </si>
+  <si>
+    <t>MARIAM ABRIL</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>NOE</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>MERIELING YAMILETH</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
   <si>
     <t>PAULINA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BRISEÑO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DONJUAN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SUSUNAGA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>AURORA</t>
-  </si>
-  <si>
-    <t>EVELYN AISHA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>OFELIA</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>RAUL ANTONIO</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>GISELA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
-  </si>
-  <si>
-    <t>MARIAM ABRIL</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>NOE</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>MERIELING YAMILETH</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
   </si>
 </sst>
 </file>
@@ -974,7 +974,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -992,7 +992,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1051,7 +1051,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1092,7 +1092,7 @@
         <v>5</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1110,7 +1110,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1128,7 +1128,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1146,7 +1146,7 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1205,7 +1205,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1223,7 +1223,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1282,7 +1282,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1359,7 +1359,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1436,7 +1436,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1454,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1513,7 +1513,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1590,7 +1590,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1667,7 +1667,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1685,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1744,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1821,7 +1821,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1898,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1975,7 +1975,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2052,7 +2052,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -2070,7 +2070,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2129,7 +2129,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2206,7 +2206,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2283,7 +2283,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2360,7 +2360,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>6</v>
@@ -2437,7 +2437,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2514,7 +2514,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2532,7 +2532,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2591,7 +2591,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2609,7 +2609,7 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2668,7 +2668,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2727,7 +2727,7 @@
         <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2745,7 +2745,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2763,7 +2763,7 @@
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2822,7 +2822,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2899,7 +2899,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>5</v>
@@ -2958,7 +2958,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2976,7 +2976,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -3053,7 +3053,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>5</v>
@@ -3112,7 +3112,7 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3130,7 +3130,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>5</v>
@@ -3148,7 +3148,7 @@
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3207,7 +3207,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3266,7 +3266,7 @@
         <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3284,7 +3284,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>5</v>
@@ -3302,7 +3302,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3361,7 +3361,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>5</v>
@@ -3402,7 +3402,7 @@
         <v>5</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3420,7 +3420,7 @@
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3438,7 +3438,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3456,7 +3456,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3684,22 +3684,22 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>90.91</v>
       </c>
       <c r="G7">
+        <v>9.09</v>
+      </c>
+      <c r="H7">
+        <v>7.5</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>7.7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
       <c r="J7">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3709,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3744,30 +3744,30 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920360</v>
+        <v>19330051920386</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3778,82 +3778,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920386</v>
+        <v>19330051920434</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920386</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920434</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920399</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3895,13 +3835,13 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3912,13 +3852,13 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3929,10 +3869,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3940,30 +3880,30 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920399</v>
+        <v>19330051920359</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920359</v>
+        <v>19330051920358</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
         <v>113</v>
@@ -3974,13 +3914,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920358</v>
+        <v>19330051920456</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
         <v>114</v>
@@ -3991,13 +3931,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920456</v>
+        <v>19330051920362</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
         <v>115</v>
@@ -4008,13 +3948,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920362</v>
+        <v>19330051920426</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>116</v>
@@ -4025,13 +3965,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920426</v>
+        <v>19330051920366</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>117</v>
@@ -4042,16 +3982,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920366</v>
+        <v>19330051920365</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4059,13 +3999,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920365</v>
+        <v>19330051920368</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
         <v>118</v>
@@ -4076,13 +4016,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920368</v>
+        <v>19330051920367</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
         <v>119</v>
@@ -4093,13 +4033,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920367</v>
+        <v>19330051920371</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
         <v>120</v>
@@ -4110,13 +4050,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920371</v>
+        <v>18330051920097</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
         <v>121</v>
@@ -4127,16 +4067,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>18330051920097</v>
+        <v>19330051920372</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4144,16 +4084,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920372</v>
+        <v>19330051920373</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4161,13 +4101,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920373</v>
+        <v>19330051920375</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>123</v>
@@ -4178,13 +4118,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920375</v>
+        <v>19330051920374</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
         <v>124</v>
@@ -4195,13 +4135,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920374</v>
+        <v>19330051920376</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
         <v>125</v>
@@ -4212,13 +4152,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920376</v>
+        <v>19330051920377</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
         <v>126</v>
@@ -4229,13 +4169,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920377</v>
+        <v>19330051920378</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
         <v>127</v>
@@ -4246,13 +4186,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920378</v>
+        <v>19330051920381</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
         <v>128</v>
@@ -4263,13 +4203,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920381</v>
+        <v>19330051920382</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
         <v>129</v>
@@ -4280,13 +4220,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920382</v>
+        <v>19330051920383</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
         <v>130</v>
@@ -4297,13 +4237,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920383</v>
+        <v>19330051920389</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
         <v>131</v>
@@ -4314,13 +4254,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920389</v>
+        <v>19330051920436</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
         <v>132</v>
@@ -4331,13 +4271,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920436</v>
+        <v>19330051920391</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
         <v>133</v>
@@ -4348,13 +4288,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920391</v>
+        <v>19330051920393</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
         <v>134</v>
@@ -4365,13 +4305,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920393</v>
+        <v>19330051920394</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
         <v>135</v>
@@ -4382,13 +4322,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920394</v>
+        <v>19330051920396</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
@@ -4399,13 +4339,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920396</v>
+        <v>19330051920369</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
         <v>137</v>
@@ -4416,13 +4356,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920369</v>
+        <v>19330051920398</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
         <v>138</v>
@@ -4433,13 +4373,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920398</v>
+        <v>19330051920399</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
         <v>139</v>
@@ -4490,13 +4430,13 @@
         <v>19330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4513,13 +4453,13 @@
         <v>19330051920367</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -4536,13 +4476,13 @@
         <v>19330051920375</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4559,13 +4499,13 @@
         <v>19330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -4582,13 +4522,13 @@
         <v>19330051920394</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4605,13 +4545,13 @@
         <v>19330051920396</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -4628,13 +4568,13 @@
         <v>19330051920398</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
         <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>

--- a/grupos/6ARHV - Estadisticos 20212.xlsx
+++ b/grupos/6ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -182,21 +182,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,223 +209,223 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>BRETON</t>
   </si>
   <si>
+    <t>BRISEÑO</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DONJUAN</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>VICENTE</t>
   </si>
   <si>
+    <t>SUSUNAGA</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>MELCHOR</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>AQUINO</t>
   </si>
   <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>VOTTE</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>AURORA</t>
+  </si>
+  <si>
+    <t>EVELYN AISHA</t>
+  </si>
+  <si>
     <t>AMYRA NAHOMY</t>
   </si>
   <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOEL</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>OFELIA</t>
+  </si>
+  <si>
+    <t>ZURI SADAY</t>
+  </si>
+  <si>
+    <t>RAUL ANTONIO</t>
+  </si>
+  <si>
+    <t>HILARIO</t>
+  </si>
+  <si>
+    <t>GISELA</t>
+  </si>
+  <si>
+    <t>MARIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>DARIANA MONSERRAT</t>
+  </si>
+  <si>
+    <t>MARIAM ABRIL</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>LUIS HUGO</t>
   </si>
   <si>
+    <t>GUADALUPE</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>NOE</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>MERIELING YAMILETH</t>
+  </si>
+  <si>
     <t>SAIRA YAMILET</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BRISEÑO</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DONJUAN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>SUSUNAGA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>AURORA</t>
-  </si>
-  <si>
-    <t>EVELYN AISHA</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOEL</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>OFELIA</t>
-  </si>
-  <si>
-    <t>ZURI SADAY</t>
-  </si>
-  <si>
-    <t>RAUL ANTONIO</t>
-  </si>
-  <si>
-    <t>HILARIO</t>
-  </si>
-  <si>
-    <t>GISELA</t>
-  </si>
-  <si>
-    <t>MARIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>DARIANA MONSERRAT</t>
-  </si>
-  <si>
-    <t>MARIAM ABRIL</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>NOE</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>MERIELING YAMILETH</t>
   </si>
   <si>
     <t>ELIZABETH</t>
@@ -944,7 +944,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -959,37 +959,37 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>6</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1036,19 +1036,19 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -1095,7 +1095,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -1104,7 +1104,7 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -1113,25 +1113,25 @@
         <v>4</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>5</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1140,7 +1140,7 @@
         <v>5</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1190,37 +1190,37 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>10</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>7</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1267,19 +1267,19 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1291,13 +1291,13 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1326,7 +1326,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>8</v>
@@ -1344,37 +1344,37 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>8</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1403,10 +1403,10 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>9</v>
@@ -1421,37 +1421,37 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>10</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1498,34 +1498,34 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>6</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1575,19 +1575,19 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>6</v>
@@ -1602,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1634,10 +1634,10 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -1652,28 +1652,28 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
         <v>8</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1729,19 +1729,19 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1753,13 +1753,13 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1806,19 +1806,19 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -1830,13 +1830,13 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>10</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1883,19 +1883,19 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -1904,16 +1904,16 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1960,37 +1960,37 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>10</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>7</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2019,7 +2019,7 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>8</v>
@@ -2037,25 +2037,25 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>10</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2064,7 +2064,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2114,34 +2114,34 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2191,25 +2191,25 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>7</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2218,7 +2218,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2268,19 +2268,19 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>10</v>
@@ -2292,13 +2292,13 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2327,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2345,37 +2345,37 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>10</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2422,19 +2422,19 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2499,37 +2499,37 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>10</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>7</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>9</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>9</v>
@@ -2561,7 +2561,7 @@
         <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -2576,37 +2576,37 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>10</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2635,10 +2635,10 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>8</v>
@@ -2653,34 +2653,34 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
         <v>7</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>7</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2703,7 +2703,7 @@
         <v>5</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -2712,7 +2712,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -2721,7 +2721,7 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -2730,19 +2730,19 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>5</v>
@@ -2757,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2807,19 +2807,19 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>10</v>
@@ -2869,7 +2869,7 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -2884,37 +2884,37 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>7</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2943,7 +2943,7 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>7</v>
@@ -2961,19 +2961,19 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>6</v>
@@ -3023,7 +3023,7 @@
         <v>5</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>7</v>
@@ -3038,37 +3038,37 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>7</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>6</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3088,7 +3088,7 @@
         <v>5</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -3106,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -3115,19 +3115,19 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>5</v>
@@ -3142,7 +3142,7 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3192,19 +3192,19 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -3219,7 +3219,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3269,25 +3269,25 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
         <v>5</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>8</v>
@@ -3328,7 +3328,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>8</v>
@@ -3346,37 +3346,37 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
         <v>9</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>8</v>
@@ -3405,7 +3405,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>5</v>
@@ -3423,37 +3423,37 @@
         <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>5</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>5</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3521,19 +3521,19 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>66.67</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G2">
-        <v>33.33</v>
+        <v>18.18</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3553,19 +3553,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>69.7</v>
+        <v>87.88</v>
       </c>
       <c r="G3">
-        <v>30.3</v>
+        <v>12.12</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3585,51 +3585,51 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>72.73</v>
+        <v>90.91</v>
       </c>
       <c r="G4">
-        <v>18.18</v>
+        <v>9.09</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5">
         <v>33</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>78.79000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="G5">
-        <v>21.21</v>
+        <v>9.09</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3649,19 +3649,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="G6">
-        <v>18.18</v>
+        <v>9.09</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3672,7 +3672,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3693,7 +3693,7 @@
         <v>9.09</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3709,7 +3709,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3734,66 +3734,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920360</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920386</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920434</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3829,64 +3769,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920360</v>
+        <v>19330051920359</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920386</v>
+        <v>19330051920358</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920434</v>
+        <v>19330051920360</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920359</v>
+        <v>19330051920456</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
         <v>112</v>
@@ -3897,13 +3837,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920358</v>
+        <v>19330051920362</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
         <v>113</v>
@@ -3914,13 +3854,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920456</v>
+        <v>19330051920426</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
         <v>114</v>
@@ -3931,13 +3871,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920362</v>
+        <v>19330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
         <v>115</v>
@@ -3948,16 +3888,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920426</v>
+        <v>19330051920365</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -3965,16 +3905,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920366</v>
+        <v>19330051920368</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3982,13 +3922,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920365</v>
+        <v>19330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
         <v>117</v>
@@ -3999,13 +3939,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920368</v>
+        <v>19330051920371</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
         <v>118</v>
@@ -4016,13 +3956,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920367</v>
+        <v>18330051920097</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
         <v>119</v>
@@ -4033,16 +3973,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920371</v>
+        <v>19330051920372</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4050,16 +3990,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>18330051920097</v>
+        <v>19330051920373</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4067,16 +4007,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920372</v>
+        <v>19330051920375</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4084,13 +4024,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920373</v>
+        <v>19330051920374</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>122</v>
@@ -4101,13 +4041,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920375</v>
+        <v>19330051920376</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
         <v>123</v>
@@ -4118,13 +4058,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920374</v>
+        <v>19330051920377</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
         <v>124</v>
@@ -4135,13 +4075,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920376</v>
+        <v>19330051920378</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s">
         <v>125</v>
@@ -4152,13 +4092,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920377</v>
+        <v>19330051920381</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
         <v>126</v>
@@ -4169,13 +4109,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920378</v>
+        <v>19330051920382</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>127</v>
@@ -4186,13 +4126,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920381</v>
+        <v>19330051920383</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
         <v>128</v>
@@ -4203,13 +4143,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920382</v>
+        <v>19330051920386</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
         <v>129</v>
@@ -4220,13 +4160,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920383</v>
+        <v>19330051920389</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
         <v>130</v>
@@ -4237,13 +4177,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920389</v>
+        <v>19330051920436</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
         <v>131</v>
@@ -4254,13 +4194,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920436</v>
+        <v>19330051920391</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
         <v>132</v>
@@ -4271,13 +4211,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920391</v>
+        <v>19330051920393</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s">
         <v>133</v>
@@ -4288,13 +4228,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920393</v>
+        <v>19330051920394</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
         <v>134</v>
@@ -4305,13 +4245,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920394</v>
+        <v>19330051920434</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s">
         <v>135</v>
@@ -4325,10 +4265,10 @@
         <v>19330051920396</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>136</v>
@@ -4342,10 +4282,10 @@
         <v>19330051920369</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
         <v>137</v>
@@ -4359,10 +4299,10 @@
         <v>19330051920398</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
         <v>138</v>
@@ -4376,10 +4316,10 @@
         <v>19330051920399</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
         <v>139</v>
@@ -4395,7 +4335,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4427,22 +4367,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920366</v>
+        <v>19330051920358</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4450,139 +4390,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920367</v>
+        <v>19330051920369</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920375</v>
-      </c>
-      <c r="B4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920382</v>
-      </c>
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920394</v>
-      </c>
-      <c r="B6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920396</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920398</v>
-      </c>
-      <c r="B8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>
